--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.45418476154951</v>
+        <v>7.061305023751796</v>
       </c>
       <c r="D2" t="n">
-        <v>31.69898842839518</v>
+        <v>5.151085619614216</v>
       </c>
       <c r="E2" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F2" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.67043198536471</v>
+        <v>4.658945197621765</v>
       </c>
       <c r="D3" t="n">
-        <v>34.78318121596768</v>
+        <v>5.652266947594748</v>
       </c>
       <c r="E3" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F3" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.11656246666875</v>
+        <v>4.081441400833672</v>
       </c>
       <c r="D4" t="n">
-        <v>26.50156936805031</v>
+        <v>4.306505022308176</v>
       </c>
       <c r="E4" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F4" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.62758543434209</v>
+        <v>2.70198263308059</v>
       </c>
       <c r="D5" t="n">
-        <v>26.86919660877775</v>
+        <v>4.366244448926384</v>
       </c>
       <c r="E5" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F5" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.17631468817083</v>
+        <v>5.716151136827761</v>
       </c>
       <c r="D6" t="n">
-        <v>20.39356631864323</v>
+        <v>3.313954526779525</v>
       </c>
       <c r="E6" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F6" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.38907589523028</v>
+        <v>7.05072483297492</v>
       </c>
       <c r="D7" t="n">
-        <v>25.68099695738524</v>
+        <v>4.173162005575101</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F7" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.65898890117216</v>
+        <v>2.057085696440477</v>
       </c>
       <c r="D8" t="n">
-        <v>6.37051675561956</v>
+        <v>1.035208972788179</v>
       </c>
       <c r="E8" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F8" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.725556371157419</v>
+        <v>1.417902910313081</v>
       </c>
       <c r="D9" t="n">
-        <v>3.301787693074047</v>
+        <v>0.5365405001245326</v>
       </c>
       <c r="E9" t="n">
-        <v>12.54563630048433</v>
+        <v>2.038665898828704</v>
       </c>
       <c r="F9" t="n">
-        <v>10.67396095053632</v>
+        <v>1.734518654462152</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
